--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92552836316</v>
+        <v>46157.93105886799</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93105886799</v>
+        <v>46157.93131680317</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93131680317</v>
+        <v>46157.93379641623</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93379641623</v>
+        <v>46157.93690069739</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93690069739</v>
+        <v>46158.28202931603</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28202931603</v>
+        <v>46158.2973369647</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2973369647</v>
+        <v>46158.29802200999</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29802200999</v>
+        <v>46158.33366618554</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33366618554</v>
+        <v>46158.37218470469</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.7_Вложения_ГАС/Attachments_taganai89@yandex.ru_2026-04-28_16-35-40/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37218470469</v>
+        <v>46158.37273513289</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
